--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12578,16 +12578,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12628,16 +12628,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="8">
@@ -12653,16 +12653,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.07</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="9">
@@ -12678,16 +12678,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>41.44</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -12753,16 +12753,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -12778,16 +12778,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.07</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -12803,16 +12803,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.44</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="15">
@@ -12828,16 +12828,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>50.43</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="16">
@@ -12878,16 +12878,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -429,12 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>บางจาก</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>บางจาก พรุ่งนี้</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -466,6 +472,7 @@
       <c r="C2" s="2" t="n">
         <v>37.19</v>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,11 +481,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42.94</v>
+        <v>43.54</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>42.94</v>
       </c>
+      <c r="D3" s="2" t="n">
+        <v>43.54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -492,6 +502,7 @@
       <c r="C4" s="2" t="n">
         <v>50.05</v>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +514,7 @@
       <c r="C5" s="2" t="n">
         <v>31.63</v>
       </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -516,6 +528,7 @@
       <c r="C6" s="2" t="n">
         <v>35.69</v>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -524,11 +537,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>41.07</v>
+        <v>41.67</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>41.07</v>
       </c>
+      <c r="D7" s="2" t="n">
+        <v>41.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,11 +553,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>41.44</v>
+        <v>42.04</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>41.44</v>
       </c>
+      <c r="D8" s="2" t="n">
+        <v>42.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -553,6 +572,7 @@
         <v>47.79</v>
       </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -561,9 +581,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>50.43</v>
+        <v>51.03</v>
       </c>
       <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -577,6 +598,7 @@
       <c r="C11" s="2" t="n">
         <v>49.29</v>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -666,7 +688,7 @@
         <v>37.19</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>42.94</v>
+        <v>43.54</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>50.05</v>
@@ -675,16 +697,16 @@
         <v>35.69</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>41.07</v>
+        <v>41.67</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41.44</v>
+        <v>42.04</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>47.79</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>50.43</v>
+        <v>51.03</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>49.79</v>
@@ -12737,7 +12759,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42.94</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="12">
@@ -12812,7 +12834,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.07</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -12837,7 +12859,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>41.44</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -12887,7 +12909,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.43</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12643,16 +12643,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12668,16 +12668,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12693,16 +12693,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -12718,16 +12718,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -12743,16 +12743,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -12818,16 +12818,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -12843,16 +12843,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -12868,16 +12868,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -12893,16 +12893,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -12943,16 +12943,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12708,16 +12708,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12733,16 +12733,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12758,16 +12758,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -12783,16 +12783,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -12808,16 +12808,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -12883,16 +12883,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -12908,16 +12908,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -12933,16 +12933,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -12958,16 +12958,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13008,16 +13008,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12773,16 +12773,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12798,16 +12798,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12823,16 +12823,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -12848,16 +12848,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -12873,16 +12873,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -12948,16 +12948,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -12973,16 +12973,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -12998,16 +12998,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -13023,16 +13023,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13073,16 +13073,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12838,16 +12838,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12863,16 +12863,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12888,16 +12888,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -12913,16 +12913,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -12938,16 +12938,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -13013,16 +13013,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -13038,16 +13038,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -13063,16 +13063,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -13088,16 +13088,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13138,16 +13138,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -12903,16 +12903,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -12928,16 +12928,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -12953,16 +12953,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -12978,16 +12978,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -13003,16 +13003,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -13078,16 +13078,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -13103,16 +13103,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -13128,16 +13128,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -13153,16 +13153,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13203,16 +13203,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -13033,16 +13033,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -13058,16 +13058,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -13083,16 +13083,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.69</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -13108,16 +13108,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -13133,16 +13133,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -13208,16 +13208,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.69</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -13233,16 +13233,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="14">
@@ -13258,16 +13258,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -13283,16 +13283,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13333,16 +13333,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -13098,16 +13098,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -13123,16 +13123,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7">
@@ -13148,16 +13148,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.5</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -13173,16 +13173,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="9">
@@ -13198,16 +13198,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="10">
@@ -13273,16 +13273,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33.5</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="13">
@@ -13298,16 +13298,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.67</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="14">
@@ -13323,16 +13323,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42.04</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -13348,16 +13348,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="16">
@@ -13398,16 +13398,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -429,13 +429,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,11 +453,6 @@
           <t>บางจาก</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>บางจาก พรุ่งนี้</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,7 +466,6 @@
       <c r="C2" s="2" t="n">
         <v>33.5</v>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,9 +477,6 @@
         <v>42.54</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>43.54</v>
-      </c>
-      <c r="D3" s="2" t="n">
         <v>42.54</v>
       </c>
     </row>
@@ -500,9 +490,6 @@
         <v>49.05</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="D4" s="2" t="n">
         <v>49.05</v>
       </c>
     </row>
@@ -516,7 +503,6 @@
       <c r="C5" s="2" t="n">
         <v>31.63</v>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -530,7 +516,6 @@
       <c r="C6" s="2" t="n">
         <v>33.5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -542,9 +527,6 @@
         <v>41.17</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="D7" s="2" t="n">
         <v>41.17</v>
       </c>
     </row>
@@ -558,9 +540,6 @@
         <v>41.54</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="D8" s="2" t="n">
         <v>41.54</v>
       </c>
     </row>
@@ -574,7 +553,6 @@
         <v>47.05</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,7 +564,6 @@
         <v>51.03</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -598,9 +575,6 @@
         <v>49.05</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="D11" s="2" t="n">
         <v>48.55</v>
       </c>
     </row>
@@ -12722,10 +12696,10 @@
         <v>33.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43.54</v>
+        <v>42.54</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>50.05</v>
+        <v>49.05</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>31.63</v>
@@ -12734,13 +12708,13 @@
         <v>33.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41.67</v>
+        <v>41.17</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>42.04</v>
+        <v>41.54</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>49.29</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="3">
@@ -13148,7 +13122,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43.54</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="4">
@@ -13173,7 +13147,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50.05</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="5">
@@ -13189,16 +13163,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.29</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -13214,16 +13188,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7">
@@ -13239,16 +13213,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.5</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="8">
@@ -13264,16 +13238,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.67</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="9">
@@ -13289,16 +13263,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.04</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="10">
@@ -13364,16 +13338,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33.5</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="13">
@@ -13389,16 +13363,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.17</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="14">
@@ -13414,16 +13388,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.54</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="15">
@@ -13439,16 +13413,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="16">
@@ -13489,16 +13463,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -13228,16 +13228,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>48.55</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -13253,16 +13253,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7">
@@ -13278,16 +13278,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.5</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="8">
@@ -13303,16 +13303,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.17</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="9">
@@ -13328,16 +13328,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>41.54</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="10">
@@ -13403,16 +13403,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33.5</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="13">
@@ -13428,16 +13428,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.17</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="14">
@@ -13453,16 +13453,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.54</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="15">
@@ -13478,16 +13478,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="16">
@@ -13528,16 +13528,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">

--- a/data/thai-oil-prices.xlsx
+++ b/data/thai-oil-prices.xlsx
@@ -13293,16 +13293,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>เบนซินพรีเมียม 98+</t>
+          <t>แก๊สโซฮอล์ E85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ไฮ พรีเมียม 98 พลัส</t>
+          <t>แก๊สโซฮอล์ E85 S EVO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>48.55</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="6">
@@ -13318,16 +13318,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E85 S EVO</t>
+          <t>แก๊สโซฮอล์ E20 S EVO</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.63</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7">
@@ -13343,16 +13343,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20 S EVO</t>
+          <t>แก๊สโซฮอล์ 91 S EVO</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.5</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="8">
@@ -13368,16 +13368,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91 S EVO</t>
+          <t>แก๊สโซฮอล์ 95 S EVO</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.17</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="9">
@@ -13393,16 +13393,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>เบนซินพรีเมียม 98+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95 S EVO</t>
+          <t>ไฮ พรีเมียม 98 พลัส</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>41.54</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="10">
@@ -13468,16 +13468,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ E20</t>
+          <t>ดีเซลพรีเมียม</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ E20</t>
+          <t>Super Power Diesel</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33.5</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="13">
@@ -13493,16 +13493,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 91</t>
+          <t>แก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 91</t>
+          <t>เบนซินแก๊สโซฮอล์ E20</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41.17</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="14">
@@ -13518,16 +13518,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>แก๊สโซฮอล์ 95</t>
+          <t>แก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>เบนซินแก๊สโซฮอล์ 95</t>
+          <t>เบนซินแก๊สโซฮอล์ 91</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41.54</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="15">
@@ -13543,16 +13543,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>เบนซิน 95</t>
+          <t>แก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>เบนซิน</t>
+          <t>เบนซินแก๊สโซฮอล์ 95</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.03</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="16">
@@ -13593,16 +13593,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ดีเซลพรีเมียม</t>
+          <t>เบนซิน 95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Super Power Diesel</t>
+          <t>เบนซิน</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49.05</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="18">
